--- a/raw/processedSamples/20260407_r1_SG_USDA-Nasal-swabs_RT-QuIC.xlsx
+++ b/raw/processedSamples/20260407_r1_SG_USDA-Nasal-swabs_RT-QuIC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MNPRO\Desktop\RT-QuIC Data\Sarah's RT-QuIC Data\2026\20260407_r1_SG_USDA-Nasal-swabs_RT-QuIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\processedSamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77C9C05C-B015-4242-A63E-B419D5565B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1D0173-0CAA-45E4-9885-AA883EF5A620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5670" yWindow="3240" windowWidth="21600" windowHeight="11295" xr2:uid="{0DE0FADC-4ACF-434D-971F-DAAEA05AF0B2}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0DE0FADC-4ACF-434D-971F-DAAEA05AF0B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="170">
   <si>
     <t>User: USER</t>
   </si>
@@ -547,6 +547,9 @@
   </si>
   <si>
     <t>3. Dilutions</t>
+  </si>
+  <si>
+    <t>Dilutions</t>
   </si>
 </sst>
 </file>
@@ -2343,7 +2346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EC67451-92E7-4ABE-A402-656E82C50022}">
-  <dimension ref="A1:CT302"/>
+  <dimension ref="A1:CT303"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:98" x14ac:dyDescent="0.25">
@@ -88814,6 +88817,300 @@
         <v>156</v>
       </c>
     </row>
+    <row r="303" spans="1:98" ht="30" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B303" s="3"/>
+      <c r="C303" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D303" s="4">
+        <v>10</v>
+      </c>
+      <c r="E303" s="4">
+        <v>10</v>
+      </c>
+      <c r="F303" s="4">
+        <v>10</v>
+      </c>
+      <c r="G303" s="4">
+        <v>10</v>
+      </c>
+      <c r="H303" s="4">
+        <v>10</v>
+      </c>
+      <c r="I303" s="4">
+        <v>10</v>
+      </c>
+      <c r="J303" s="4">
+        <v>10</v>
+      </c>
+      <c r="K303" s="4">
+        <v>10</v>
+      </c>
+      <c r="L303" s="4">
+        <v>10</v>
+      </c>
+      <c r="M303" s="4">
+        <v>10</v>
+      </c>
+      <c r="N303" s="4">
+        <v>10</v>
+      </c>
+      <c r="O303" s="4">
+        <v>1000</v>
+      </c>
+      <c r="P303" s="4">
+        <v>10</v>
+      </c>
+      <c r="Q303" s="4">
+        <v>10</v>
+      </c>
+      <c r="R303" s="4">
+        <v>10</v>
+      </c>
+      <c r="S303" s="4">
+        <v>10</v>
+      </c>
+      <c r="T303" s="4">
+        <v>10</v>
+      </c>
+      <c r="U303" s="4">
+        <v>10</v>
+      </c>
+      <c r="V303" s="4">
+        <v>10</v>
+      </c>
+      <c r="W303" s="4">
+        <v>10</v>
+      </c>
+      <c r="X303" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y303" s="4">
+        <v>10</v>
+      </c>
+      <c r="Z303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AA303" s="4">
+        <v>1000</v>
+      </c>
+      <c r="AB303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AC303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AD303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AE303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AF303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AG303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AH303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AI303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AJ303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AK303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AL303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AM303" s="4">
+        <v>1000</v>
+      </c>
+      <c r="AN303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AO303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AP303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AQ303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AR303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AS303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AT303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AU303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AV303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AW303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AX303" s="4">
+        <v>10</v>
+      </c>
+      <c r="AY303" s="4">
+        <v>1000</v>
+      </c>
+      <c r="AZ303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BA303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BB303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BC303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BD303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BE303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BF303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BG303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BH303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BI303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BJ303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BK303" s="4">
+        <v>1000</v>
+      </c>
+      <c r="BL303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BM303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BN303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BO303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BP303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BQ303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BR303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BS303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BT303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BU303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BV303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BW303" s="4">
+        <v>1000</v>
+      </c>
+      <c r="BX303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BY303" s="4">
+        <v>10</v>
+      </c>
+      <c r="BZ303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CA303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CB303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CC303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CD303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CE303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CF303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CG303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CH303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CI303" s="4">
+        <v>1000</v>
+      </c>
+      <c r="CJ303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CK303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CL303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CM303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CN303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CO303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CP303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CQ303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CR303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CS303" s="4">
+        <v>10</v>
+      </c>
+      <c r="CT303" s="5">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
